--- a/data/synthetic/messy_foyle/bookings summer NEW.xlsx
+++ b/data/synthetic/messy_foyle/bookings summer NEW.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t xml:space="preserve">Request Received </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,12 +517,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>booking confirmed</t>
+          <t>BOOKING CONFIRMED</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>invoice issued</t>
+          <t xml:space="preserve">Invoice Issued </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Arrival Logistics </t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -598,39 +598,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrival </t>
+          <t>pre-arrival logistics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B-2026-012</t>
+          <t>B-2026-011</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t>ARRIVAL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>placement offer</t>
+          <t xml:space="preserve">Request Received </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>booking confirmed</t>
+          <t>PLACEMENT OFFER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice Issued </t>
+          <t>Booking Confirmed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Arrival Logistics </t>
+          <t>invoice issued</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARRIVAL</t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -775,24 +775,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B-2026-013</t>
+          <t>B-2026-012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request Received </t>
+          <t>Pre-Arrival Logistics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,34 +802,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B-2026-013</t>
+          <t>B-2026-012</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Placement Offer</t>
+          <t>ARRIVAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Placement Re-allocation</t>
+          <t xml:space="preserve">Request Received </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>chased 2x</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Booking Confirmed</t>
+          <t>Placement Offer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -895,22 +895,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Invoice Issued</t>
+          <t xml:space="preserve">Booking Confirmed </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pre-arrival logistics</t>
+          <t>placement offer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>waiting on family</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrival </t>
+          <t>invoice issued</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,17 +971,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B-2026-014</t>
+          <t>B-2026-013</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t>DOCUMENT COLLECTION</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -998,17 +998,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B-2026-014</t>
+          <t>B-2026-013</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>placement offer</t>
+          <t>PRE-ARRIVAL LOGISTICS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1018,24 +1018,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B-2026-014</t>
+          <t>B-2026-013</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking Confirmed </t>
+          <t xml:space="preserve">Arrival </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Invoice Issued</t>
+          <t xml:space="preserve">Request Received </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PRE-ARRIVAL LOGISTICS</t>
+          <t>Placement Offer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arrival</t>
+          <t>booking confirmed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,115 +1126,115 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B-2026-015</t>
+          <t>B-2026-014</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>request received</t>
+          <t>INVOICE ISSUED</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B-2026-015</t>
+          <t>B-2026-014</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PLACEMENT OFFER</t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B-2026-015</t>
+          <t>B-2026-014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Booking Confirmed</t>
+          <t>Pre-Arrival Logistics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B-2026-015</t>
+          <t>B-2026-014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INVOICE ISSUED</t>
+          <t xml:space="preserve">Arrival </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1246,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Document Re-request</t>
+          <t>Request Received</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1273,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pre-Arrival Logistics</t>
+          <t>Placement Offer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrival </t>
+          <t>booking confirmed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1315,78 +1315,78 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B-2026-016</t>
+          <t>B-2026-015</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t>invoice issued</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B-2026-016</t>
+          <t>B-2026-015</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>placement offer</t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B-2026-016</t>
+          <t>B-2026-015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BOOKING CONFIRMED</t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1396,24 +1396,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>waiting on family</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B-2026-016</t>
+          <t>B-2026-015</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Invoice Issued</t>
+          <t>PRE-ARRIVAL LOGISTICS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1423,24 +1423,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B-2026-016</t>
+          <t>B-2026-015</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pre-Arrival Logistics</t>
+          <t>ARRIVAL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>
@@ -1462,71 +1462,71 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arrival </t>
+          <t>Request Received</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B-2026-017</t>
+          <t>B-2026-016</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Request Received</t>
+          <t>PLACEMENT OFFER</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B-2026-017</t>
+          <t>B-2026-016</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Placement Offer</t>
+          <t>Booking Confirmed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1538,61 +1538,61 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B-2026-017</t>
+          <t>B-2026-016</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>booking confirmed</t>
+          <t>Invoice Issued</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B-2026-017</t>
+          <t>B-2026-016</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>invoice issued</t>
+          <t>Document Collection</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B-2026-017</t>
+          <t>B-2026-016</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1612,14 +1612,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B-2026-017</t>
+          <t>B-2026-016</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1646,125 +1646,125 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B-2026-018</t>
+          <t>B-2026-017</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>REQUEST RECEIVED</t>
+          <t>request received</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Sean Doyle</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B-2026-018</t>
+          <t>B-2026-017</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PLACEMENT OFFER</t>
+          <t xml:space="preserve">Placement Offer </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Aoife Brennan</t>
+          <t>Marta Kowalska</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>DONE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B-2026-018</t>
+          <t>B-2026-017</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booking Confirmed </t>
+          <t>BOOKING CONFIRMED</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sean Doyle</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">done </t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B-2026-018</t>
+          <t>B-2026-017</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Invoice Issued</t>
+          <t>INVOICE ISSUED</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Marta Kowalska</t>
+          <t>Aoife Brennan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Completed ✔</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B-2026-018</t>
+          <t>B-2026-017</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pre-Arrival Logistics</t>
+          <t>DOCUMENT COLLECTION</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1774,34 +1774,250 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>Completed ✔</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>B-2026-017</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pre-Arrival Logistics</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B-2026-017</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>B-2026-018</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Arrival</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request Received </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>B-2026-018</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PLACEMENT OFFER</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B-2026-018</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Booking Confirmed</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>B-2026-018</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Invoice Issued</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sean Doyle</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>B-2026-018</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Document Collection </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B-2026-018</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pre-Arrival Logistics</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sean Doyle</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>B-2026-018</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ARRIVAL</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Sean Doyle</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Completed ✔</t>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
         </is>
       </c>
     </row>

--- a/data/synthetic/messy_foyle/bookings summer NEW.xlsx
+++ b/data/synthetic/messy_foyle/bookings summer NEW.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2007,17 +2007,896 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B-2026-019</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request Received </t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>B-2026-020</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>request received</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>chased 2x</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>B-2026-021</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>request received</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>B-2026-021</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Placement Offer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>waiting on family</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>B-2026-022</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>REQUEST RECEIVED</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B-2026-022</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PLACEMENT OFFER</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>tbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>B-2026-023</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request Received </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>B-2026-023</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placement Offer </t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B-2026-023</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BOOKING CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>B-2026-024</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request Received </t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B-2026-024</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placement Offer </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B-2026-024</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>booking confirmed</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B-2026-025</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>REQUEST RECEIVED</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B-2026-025</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Placement Offer</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B-2026-025</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Booking Confirmed</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B-2026-025</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INVOICE ISSUED</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B-2026-025</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>DOCUMENT COLLECTION</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>tbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B-2026-026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Request Received</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B-2026-026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Placement Offer</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B-2026-026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Booking Confirmed </t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B-2026-026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>INVOICE ISSUED</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B-2026-026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Document Collection </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B-2026-026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PRE-ARRIVAL LOGISTICS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B-2026-027</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request Received </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B-2026-027</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placement Offer </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">done </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>B-2026-027</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BOOKING CONFIRMED</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>B-2026-027</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>INVOICE ISSUED</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>B-2026-027</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Document Collection</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>B-2026-027</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-Arrival Logistics </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Aoife Brennan</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>tbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>B-2026-028</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Request Received </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>B-2026-028</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placement Offer </t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B-2026-028</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Booking Confirmed </t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Marta Kowalska</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Completed ✔</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>B-2026-028</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Invoice Issued</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Marta Kowalska</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">done </t>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>In progress</t>
         </is>
       </c>
     </row>
